--- a/config/capture/level.xlsx
+++ b/config/capture/level.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="9945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="level" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="level" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1227,18 +1227,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-    </row>
+    <row r="4"/>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
@@ -1247,7 +1236,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ブロンズIII</t>
+          <t>青铜III</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1304,7 +1293,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ブロンズII</t>
+          <t>青铜II</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1361,7 +1350,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ブロンズI</t>
+          <t>青铜I</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1418,7 +1407,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>シルバーIII</t>
+          <t>银色III</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1475,7 +1464,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>シルバーII</t>
+          <t>银色II</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1532,7 +1521,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>シルバーI</t>
+          <t>银色I</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1589,7 +1578,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ゴールドIII</t>
+          <t>黄金III</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1646,7 +1635,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ゴールドII</t>
+          <t>黄金II</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1703,7 +1692,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ゴールドI</t>
+          <t>黄金I</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1760,7 +1749,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>プラチナIII</t>
+          <t>铂金III</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1817,7 +1806,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>プラチナII</t>
+          <t>白金II</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1874,7 +1863,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>プラチナI</t>
+          <t>白金I</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1931,7 +1920,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ダイヤIII</t>
+          <t>钻石III</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1988,7 +1977,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ダイヤII</t>
+          <t>钻石II</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2045,7 +2034,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ダイヤI</t>
+          <t>钻石I</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2102,7 +2091,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>マスター</t>
+          <t>大师</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
